--- a/2025/ILLIA/Diciembre/ILLIA-Diciembre.xlsx
+++ b/2025/ILLIA/Diciembre/ILLIA-Diciembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2025\ILLIA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0E5517-18BF-46ED-A09B-ABEA8E8452AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F95EDA4-1ED2-4D55-B289-3E9D1A04E2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1549,7 +1549,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="27"/>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1733,8 +1733,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1762,9 +1760,7 @@
     <xf numFmtId="164" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="14" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="14" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1825,8 +1821,6 @@
     <xf numFmtId="166" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="18" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1866,9 +1860,7 @@
     <xf numFmtId="166" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="21" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="20" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="29" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1885,52 +1877,43 @@
     <xf numFmtId="164" fontId="28" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -1940,7 +1923,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1956,41 +1938,55 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="20" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="18" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2283,51 +2279,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="195"/>
-      <c r="B1" s="196"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="198"/>
+      <c r="A1" s="189"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="192"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="199"/>
-      <c r="B2" s="200" t="s">
+      <c r="A2" s="193"/>
+      <c r="B2" s="194" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="201"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="195"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="199"/>
-      <c r="B3" s="249" t="s">
+      <c r="A3" s="193"/>
+      <c r="B3" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="250"/>
-      <c r="D3" s="250"/>
-      <c r="E3" s="201"/>
+      <c r="C3" s="240"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="195"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="199"/>
-      <c r="B4" s="251"/>
-      <c r="C4" s="251"/>
-      <c r="D4" s="251"/>
-      <c r="E4" s="201"/>
+      <c r="A4" s="193"/>
+      <c r="B4" s="241"/>
+      <c r="C4" s="241"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="195"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="202" t="s">
+      <c r="A5" s="196" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -2335,52 +2331,52 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="203"/>
+      <c r="E5" s="197"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="198" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205" t="s">
+      <c r="C6" s="199"/>
+      <c r="D6" s="199" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="206"/>
+      <c r="E6" s="200"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="135"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="133"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="260" t="s">
+      <c r="A7" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="261"/>
-      <c r="C7" s="261"/>
-      <c r="D7" s="261"/>
-      <c r="E7" s="262"/>
+      <c r="B7" s="249"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="250"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="135"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="133"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="256" t="s">
+      <c r="B9" s="245" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="239"/>
+      <c r="C9" s="231"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2389,8 +2385,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2399,8 +2395,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="239"/>
-      <c r="C11" s="239"/>
+      <c r="B11" s="231"/>
+      <c r="C11" s="231"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2419,43 +2415,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="263" t="s">
+      <c r="A14" s="251" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="239"/>
-      <c r="C14" s="239"/>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239"/>
+      <c r="B14" s="231"/>
+      <c r="C14" s="231"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="231"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="239"/>
-      <c r="B15" s="239"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239"/>
-      <c r="E15" s="239"/>
+      <c r="A15" s="231"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="239"/>
-      <c r="B16" s="239"/>
-      <c r="C16" s="239"/>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
+      <c r="A16" s="231"/>
+      <c r="B16" s="231"/>
+      <c r="C16" s="231"/>
+      <c r="D16" s="231"/>
+      <c r="E16" s="231"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="239"/>
-      <c r="B17" s="239"/>
-      <c r="C17" s="239"/>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
+      <c r="A17" s="231"/>
+      <c r="B17" s="231"/>
+      <c r="C17" s="231"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2502,7 +2498,7 @@
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="155">
+      <c r="D23" s="151">
         <v>758273.64</v>
       </c>
       <c r="E23" s="13"/>
@@ -2511,7 +2507,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="155"/>
+      <c r="D24" s="151"/>
       <c r="E24" s="13"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2539,7 +2535,7 @@
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="155"/>
+      <c r="D25" s="151"/>
       <c r="E25" s="13"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="155">
+      <c r="D26" s="151">
         <v>-187672.73</v>
       </c>
       <c r="E26" s="13"/>
@@ -2580,7 +2576,7 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="155">
+      <c r="D27" s="151">
         <v>0.09</v>
       </c>
       <c r="E27" s="13"/>
@@ -2606,37 +2602,37 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" s="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>181</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
-      <c r="D28" s="155">
+      <c r="D28" s="151">
         <v>345570</v>
       </c>
       <c r="E28" s="13"/>
-      <c r="F28" s="274"/>
-      <c r="G28" s="274"/>
-      <c r="H28" s="274"/>
-      <c r="I28" s="274"/>
-      <c r="J28" s="274"/>
-      <c r="K28" s="274"/>
-      <c r="L28" s="274"/>
-      <c r="M28" s="274"/>
-      <c r="N28" s="274"/>
-      <c r="O28" s="274"/>
-      <c r="P28" s="274"/>
-      <c r="Q28" s="274"/>
-      <c r="R28" s="274"/>
-      <c r="S28" s="274"/>
-      <c r="T28" s="274"/>
-      <c r="U28" s="274"/>
-      <c r="V28" s="274"/>
-      <c r="W28" s="274"/>
-      <c r="X28" s="274"/>
-      <c r="Y28" s="274"/>
-      <c r="Z28" s="274"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="132"/>
+      <c r="M28" s="132"/>
+      <c r="N28" s="132"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="132"/>
+      <c r="Q28" s="132"/>
+      <c r="R28" s="132"/>
+      <c r="S28" s="132"/>
+      <c r="T28" s="132"/>
+      <c r="U28" s="132"/>
+      <c r="V28" s="132"/>
+      <c r="W28" s="132"/>
+      <c r="X28" s="132"/>
+      <c r="Y28" s="132"/>
+      <c r="Z28" s="132"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
@@ -2644,7 +2640,7 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="156">
+      <c r="D29" s="152">
         <f>SUM(D23:D28)</f>
         <v>916171</v>
       </c>
@@ -2672,12 +2668,12 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="272" t="s">
+      <c r="A30" s="254" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="273"/>
+      <c r="B30" s="255"/>
       <c r="C30" s="13"/>
-      <c r="D30" s="157">
+      <c r="D30" s="153">
         <v>220000</v>
       </c>
       <c r="E30" s="13"/>
@@ -2687,7 +2683,7 @@
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
-      <c r="D31" s="157"/>
+      <c r="D31" s="153"/>
       <c r="E31" s="13"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2717,7 +2713,7 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
-      <c r="D32" s="158">
+      <c r="D32" s="154">
         <f>SUM(D30:D31)</f>
         <v>220000</v>
       </c>
@@ -2750,7 +2746,7 @@
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
-      <c r="D33" s="159"/>
+      <c r="D33" s="155"/>
       <c r="E33" s="17">
         <f>D29+D32</f>
         <v>1136171</v>
@@ -2763,7 +2759,7 @@
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
-      <c r="D34" s="160"/>
+      <c r="D34" s="156"/>
       <c r="E34" s="19"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -2791,11 +2787,11 @@
       <c r="A35" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="176" t="s">
+      <c r="B35" s="172" t="s">
         <v>169</v>
       </c>
       <c r="C35" s="13"/>
-      <c r="D35" s="226">
+      <c r="D35" s="218">
         <v>35000</v>
       </c>
       <c r="E35" s="21"/>
@@ -2822,14 +2818,14 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="207" t="s">
+      <c r="A36" s="201" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="176" t="s">
+      <c r="B36" s="172" t="s">
         <v>169</v>
       </c>
       <c r="C36" s="13"/>
-      <c r="D36" s="155">
+      <c r="D36" s="151">
         <v>132700</v>
       </c>
       <c r="E36" s="21"/>
@@ -2863,7 +2859,7 @@
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
-      <c r="D37" s="161"/>
+      <c r="D37" s="157"/>
       <c r="E37" s="22">
         <f>SUM(D35:D36)</f>
         <v>167700</v>
@@ -2896,17 +2892,17 @@
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
-      <c r="D38" s="162"/>
+      <c r="D38" s="158"/>
       <c r="E38" s="23"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="257" t="s">
+      <c r="A39" s="246" t="s">
         <v>19</v>
       </c>
-      <c r="B39" s="258"/>
+      <c r="B39" s="235"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="163">
+      <c r="D39" s="159">
         <v>60679.199999999997</v>
       </c>
       <c r="E39" s="25" t="s">
@@ -2920,7 +2916,7 @@
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
-      <c r="D40" s="161"/>
+      <c r="D40" s="157"/>
       <c r="E40" s="27">
         <f>SUM(D39:D39)</f>
         <v>60679.199999999997</v>
@@ -2933,7 +2929,7 @@
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
-      <c r="D41" s="164"/>
+      <c r="D41" s="160"/>
       <c r="E41" s="29"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2961,7 +2957,7 @@
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="165"/>
+      <c r="D42" s="161"/>
       <c r="E42" s="32"/>
       <c r="F42" s="1"/>
     </row>
@@ -2971,7 +2967,7 @@
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="30"/>
-      <c r="D43" s="277">
+      <c r="D43" s="226">
         <v>400658.29</v>
       </c>
       <c r="E43" s="33" t="s">
@@ -2987,7 +2983,7 @@
         <v>23</v>
       </c>
       <c r="C44" s="13"/>
-      <c r="D44" s="165">
+      <c r="D44" s="161">
         <v>32316.92</v>
       </c>
       <c r="E44" s="33" t="s">
@@ -3024,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="13"/>
-      <c r="D45" s="163">
+      <c r="D45" s="159">
         <v>72943.990000000005</v>
       </c>
       <c r="E45" s="33" t="str">
@@ -3036,15 +3032,15 @@
       <c r="H45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="139" t="str">
+      <c r="A46" s="137" t="str">
         <f>A45</f>
         <v>Sindicatos mes de DICIEMBRE</v>
       </c>
-      <c r="B46" s="139" t="s">
+      <c r="B46" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="C46" s="139"/>
-      <c r="D46" s="278">
+      <c r="C46" s="137"/>
+      <c r="D46" s="227">
         <v>3590.77</v>
       </c>
       <c r="E46" s="34" t="str">
@@ -3056,12 +3052,12 @@
       <c r="H46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="140" t="s">
+      <c r="A47" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="166"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="162"/>
       <c r="E47" s="27">
         <f>SUM(D42:D46)</f>
         <v>509509.97</v>
@@ -3076,7 +3072,7 @@
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="28"/>
-      <c r="D48" s="164"/>
+      <c r="D48" s="160"/>
       <c r="E48" s="29"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -3101,15 +3097,15 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="252" t="s">
+      <c r="A49" s="236" t="s">
         <v>171</v>
       </c>
-      <c r="B49" s="259"/>
+      <c r="B49" s="247"/>
       <c r="C49" s="13"/>
-      <c r="D49" s="279">
+      <c r="D49" s="228">
         <v>125300</v>
       </c>
-      <c r="E49" s="142" t="s">
+      <c r="E49" s="140" t="s">
         <v>175</v>
       </c>
       <c r="F49" s="1"/>
@@ -3135,15 +3131,15 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="149" t="s">
+      <c r="A50" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="150"/>
+      <c r="B50" s="146"/>
       <c r="C50" s="13"/>
-      <c r="D50" s="279">
+      <c r="D50" s="228">
         <v>45000</v>
       </c>
-      <c r="E50" s="142" t="s">
+      <c r="E50" s="140" t="s">
         <v>174</v>
       </c>
       <c r="F50" s="1"/>
@@ -3174,10 +3170,10 @@
       </c>
       <c r="B51" s="122"/>
       <c r="C51" s="36"/>
-      <c r="D51" s="220">
+      <c r="D51" s="212">
         <v>25970.58</v>
       </c>
-      <c r="E51" s="142" t="s">
+      <c r="E51" s="140" t="s">
         <v>178</v>
       </c>
       <c r="F51" s="37"/>
@@ -3185,15 +3181,15 @@
       <c r="H51" s="37"/>
     </row>
     <row r="52" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="252" t="s">
+      <c r="A52" s="236" t="s">
         <v>172</v>
       </c>
-      <c r="B52" s="258"/>
+      <c r="B52" s="235"/>
       <c r="C52" s="20"/>
-      <c r="D52" s="280">
+      <c r="D52" s="229">
         <v>17684.560000000001</v>
       </c>
-      <c r="E52" s="142" t="s">
+      <c r="E52" s="140" t="s">
         <v>176</v>
       </c>
       <c r="F52" s="26"/>
@@ -3218,50 +3214,50 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" s="275" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="252" t="s">
+    <row r="53" spans="1:26" s="133" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="236" t="s">
         <v>159</v>
       </c>
-      <c r="B53" s="258"/>
+      <c r="B53" s="235"/>
       <c r="C53" s="20"/>
-      <c r="D53" s="280">
+      <c r="D53" s="229">
         <v>165634.69</v>
       </c>
-      <c r="E53" s="142" t="s">
+      <c r="E53" s="140" t="s">
         <v>182</v>
       </c>
-      <c r="F53" s="276"/>
-      <c r="G53" s="276"/>
-      <c r="H53" s="276"/>
-      <c r="I53" s="274"/>
-      <c r="J53" s="274"/>
-      <c r="K53" s="274"/>
-      <c r="L53" s="274"/>
-      <c r="M53" s="274"/>
-      <c r="N53" s="274"/>
-      <c r="O53" s="274"/>
-      <c r="P53" s="274"/>
-      <c r="Q53" s="274"/>
-      <c r="R53" s="274"/>
-      <c r="S53" s="274"/>
-      <c r="T53" s="274"/>
-      <c r="U53" s="274"/>
-      <c r="V53" s="274"/>
-      <c r="W53" s="274"/>
-      <c r="X53" s="274"/>
-      <c r="Y53" s="274"/>
-      <c r="Z53" s="274"/>
+      <c r="F53" s="225"/>
+      <c r="G53" s="225"/>
+      <c r="H53" s="225"/>
+      <c r="I53" s="132"/>
+      <c r="J53" s="132"/>
+      <c r="K53" s="132"/>
+      <c r="L53" s="132"/>
+      <c r="M53" s="132"/>
+      <c r="N53" s="132"/>
+      <c r="O53" s="132"/>
+      <c r="P53" s="132"/>
+      <c r="Q53" s="132"/>
+      <c r="R53" s="132"/>
+      <c r="S53" s="132"/>
+      <c r="T53" s="132"/>
+      <c r="U53" s="132"/>
+      <c r="V53" s="132"/>
+      <c r="W53" s="132"/>
+      <c r="X53" s="132"/>
+      <c r="Y53" s="132"/>
+      <c r="Z53" s="132"/>
     </row>
     <row r="54" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="252" t="s">
+      <c r="A54" s="236" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="258"/>
+      <c r="B54" s="235"/>
       <c r="C54" s="20"/>
-      <c r="D54" s="280">
+      <c r="D54" s="229">
         <v>100865.43</v>
       </c>
-      <c r="E54" s="142" t="s">
+      <c r="E54" s="140" t="s">
         <v>176</v>
       </c>
       <c r="F54" s="26"/>
@@ -3272,17 +3268,17 @@
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
-      <c r="D55" s="163"/>
+      <c r="D55" s="159"/>
       <c r="E55" s="35"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="269"/>
-      <c r="B56" s="258"/>
+      <c r="A56" s="234"/>
+      <c r="B56" s="235"/>
       <c r="C56" s="13"/>
-      <c r="D56" s="163"/>
+      <c r="D56" s="159"/>
       <c r="E56" s="35"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -3310,7 +3306,7 @@
       <c r="A57" s="13"/>
       <c r="B57" s="38"/>
       <c r="C57" s="13"/>
-      <c r="D57" s="163"/>
+      <c r="D57" s="159"/>
       <c r="E57" s="39"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -3335,11 +3331,11 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="252"/>
-      <c r="B58" s="253"/>
+      <c r="A58" s="236"/>
+      <c r="B58" s="242"/>
       <c r="C58" s="40"/>
-      <c r="D58" s="267"/>
-      <c r="E58" s="264"/>
+      <c r="D58" s="232"/>
+      <c r="E58" s="252"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -3363,11 +3359,11 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="254"/>
-      <c r="B59" s="255"/>
+      <c r="A59" s="243"/>
+      <c r="B59" s="244"/>
       <c r="C59" s="40"/>
-      <c r="D59" s="268"/>
-      <c r="E59" s="265"/>
+      <c r="D59" s="233"/>
+      <c r="E59" s="253"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -3391,10 +3387,10 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="252"/>
-      <c r="B60" s="258"/>
+      <c r="A60" s="236"/>
+      <c r="B60" s="235"/>
       <c r="C60" s="13"/>
-      <c r="D60" s="167"/>
+      <c r="D60" s="163"/>
       <c r="E60" s="41"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -3419,10 +3415,10 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="252"/>
-      <c r="B61" s="258"/>
+      <c r="A61" s="236"/>
+      <c r="B61" s="235"/>
       <c r="C61" s="13"/>
-      <c r="D61" s="167"/>
+      <c r="D61" s="163"/>
       <c r="E61" s="41"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -3447,17 +3443,17 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="252"/>
-      <c r="B62" s="258"/>
+      <c r="A62" s="236"/>
+      <c r="B62" s="235"/>
       <c r="C62" s="13"/>
-      <c r="D62" s="167"/>
+      <c r="D62" s="163"/>
       <c r="E62" s="35"/>
     </row>
     <row r="63" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13"/>
       <c r="B63" s="42"/>
       <c r="C63" s="13"/>
-      <c r="D63" s="167"/>
+      <c r="D63" s="163"/>
       <c r="E63" s="35"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3482,10 +3478,10 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="252"/>
-      <c r="B64" s="258"/>
+      <c r="A64" s="236"/>
+      <c r="B64" s="235"/>
       <c r="C64" s="13"/>
-      <c r="D64" s="167"/>
+      <c r="D64" s="163"/>
       <c r="E64" s="35"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3513,7 +3509,7 @@
       <c r="A65" s="38"/>
       <c r="B65" s="43"/>
       <c r="C65" s="13"/>
-      <c r="D65" s="167"/>
+      <c r="D65" s="163"/>
       <c r="E65" s="35"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3538,10 +3534,10 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="252"/>
-      <c r="B66" s="258"/>
+      <c r="A66" s="236"/>
+      <c r="B66" s="235"/>
       <c r="C66" s="13"/>
-      <c r="D66" s="167"/>
+      <c r="D66" s="163"/>
       <c r="E66" s="44"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -3566,10 +3562,10 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="252"/>
-      <c r="B67" s="258"/>
+      <c r="A67" s="236"/>
+      <c r="B67" s="235"/>
       <c r="C67" s="13"/>
-      <c r="D67" s="167"/>
+      <c r="D67" s="163"/>
       <c r="E67" s="44"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -3594,10 +3590,10 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="270"/>
-      <c r="B68" s="258"/>
+      <c r="A68" s="237"/>
+      <c r="B68" s="235"/>
       <c r="C68" s="45"/>
-      <c r="D68" s="167"/>
+      <c r="D68" s="163"/>
       <c r="E68" s="44"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -3627,7 +3623,7 @@
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
-      <c r="D69" s="161"/>
+      <c r="D69" s="157"/>
       <c r="E69" s="27">
         <f>SUM(D49:D54)</f>
         <v>480455.26</v>
@@ -3639,14 +3635,14 @@
       </c>
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
-      <c r="D70" s="161"/>
+      <c r="D70" s="157"/>
       <c r="E70" s="46"/>
     </row>
     <row r="71" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
-      <c r="D71" s="165"/>
+      <c r="D71" s="161"/>
       <c r="E71" s="48"/>
     </row>
     <row r="72" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3655,7 +3651,7 @@
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
-      <c r="D72" s="168"/>
+      <c r="D72" s="164"/>
       <c r="E72" s="49">
         <f>SUM(D71:D71)</f>
         <v>0</v>
@@ -3688,7 +3684,7 @@
       </c>
       <c r="B73" s="50"/>
       <c r="C73" s="16"/>
-      <c r="D73" s="159"/>
+      <c r="D73" s="155"/>
       <c r="E73" s="46">
         <f>850.17+698.43+4797.54+618.63+2.1+2364+10+1202.53+1583.5+3434+961.5+2275.93+1316.37+1224+2364.03+534+4200+154.8+1600+1200+2351.5+457.76+2442+6000</f>
         <v>42642.79</v>
@@ -3721,7 +3717,7 @@
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
-      <c r="D74" s="227">
+      <c r="D74" s="219">
         <f>60441.95</f>
         <v>60441.95</v>
       </c>
@@ -3754,7 +3750,7 @@
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
-      <c r="D75" s="163">
+      <c r="D75" s="159">
         <v>45000</v>
       </c>
       <c r="E75" s="41"/>
@@ -3786,7 +3782,7 @@
       </c>
       <c r="B76" s="52"/>
       <c r="C76" s="52"/>
-      <c r="D76" s="138"/>
+      <c r="D76" s="136"/>
       <c r="E76" s="27">
         <f>SUM(D74:D75)</f>
         <v>105441.95</v>
@@ -3821,7 +3817,7 @@
       <c r="D79" s="1"/>
       <c r="E79" s="58"/>
       <c r="F79" s="59"/>
-      <c r="H79" s="221"/>
+      <c r="H79" s="213"/>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="60" t="s">
@@ -3835,11 +3831,11 @@
         <v>3000000</v>
       </c>
       <c r="F80" s="1"/>
-      <c r="G80" s="179"/>
-      <c r="H80" s="228"/>
+      <c r="G80" s="175"/>
+      <c r="H80" s="220"/>
     </row>
     <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H81" s="221"/>
+      <c r="H81" s="213"/>
     </row>
     <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
@@ -3849,7 +3845,7 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-      <c r="H82" s="229"/>
+      <c r="H82" s="221"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -3900,9 +3896,9 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="133"/>
-      <c r="B84" s="133"/>
-      <c r="C84" s="132"/>
+      <c r="A84" s="131"/>
+      <c r="B84" s="131"/>
+      <c r="C84" s="130"/>
       <c r="D84" s="31"/>
       <c r="E84" s="47"/>
       <c r="F84" s="1"/>
@@ -3928,9 +3924,9 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="133"/>
-      <c r="B85" s="133"/>
-      <c r="C85" s="132"/>
+      <c r="A85" s="131"/>
+      <c r="B85" s="131"/>
+      <c r="C85" s="130"/>
       <c r="D85" s="31">
         <v>0</v>
       </c>
@@ -4047,13 +4043,13 @@
       <c r="Z88" s="1"/>
     </row>
     <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="191" t="s">
+      <c r="A89" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="B89" s="191"/>
-      <c r="C89" s="191"/>
-      <c r="D89" s="191"/>
-      <c r="E89" s="192"/>
+      <c r="B89" s="185"/>
+      <c r="C89" s="185"/>
+      <c r="D89" s="185"/>
+      <c r="E89" s="186"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -4280,28 +4276,28 @@
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
     </row>
-    <row r="98" spans="1:26" s="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="134"/>
-      <c r="B98" s="134"/>
-      <c r="C98" s="134"/>
-      <c r="D98" s="134"/>
-      <c r="E98" s="134"/>
-    </row>
-    <row r="99" spans="1:26" s="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="271" t="s">
+    <row r="98" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="132"/>
+      <c r="B98" s="132"/>
+      <c r="C98" s="132"/>
+      <c r="D98" s="132"/>
+      <c r="E98" s="132"/>
+    </row>
+    <row r="99" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="238" t="s">
         <v>163</v>
       </c>
-      <c r="B99" s="271"/>
-      <c r="C99" s="134"/>
-      <c r="D99" s="134"/>
-      <c r="E99" s="134"/>
-    </row>
-    <row r="100" spans="1:26" s="135" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="271"/>
-      <c r="B100" s="271"/>
-      <c r="C100" s="134"/>
-      <c r="D100" s="134"/>
-      <c r="E100" s="134"/>
+      <c r="B99" s="238"/>
+      <c r="C99" s="132"/>
+      <c r="D99" s="132"/>
+      <c r="E99" s="132"/>
+    </row>
+    <row r="100" spans="1:26" s="133" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="238"/>
+      <c r="B100" s="238"/>
+      <c r="C100" s="132"/>
+      <c r="D100" s="132"/>
+      <c r="E100" s="132"/>
     </row>
     <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
@@ -4310,18 +4306,18 @@
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
     </row>
-    <row r="102" spans="1:26" s="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="271" t="s">
+    <row r="102" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="238" t="s">
         <v>164</v>
       </c>
-      <c r="B102" s="271"/>
-      <c r="C102" s="134"/>
-      <c r="D102" s="134"/>
-      <c r="E102" s="134"/>
+      <c r="B102" s="238"/>
+      <c r="C102" s="132"/>
+      <c r="D102" s="132"/>
+      <c r="E102" s="132"/>
     </row>
     <row r="103" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="271"/>
-      <c r="B103" s="271"/>
+      <c r="A103" s="238"/>
+      <c r="B103" s="238"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -4334,37 +4330,37 @@
       <c r="E104" s="1"/>
     </row>
     <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="127" t="s">
+      <c r="A105" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="B105" s="128"/>
+      <c r="B105" s="126"/>
       <c r="C105" s="69"/>
     </row>
     <row r="106" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="131" t="s">
+      <c r="A106" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="B106" s="193">
+      <c r="B106" s="187">
         <v>3949418.1299999994</v>
       </c>
       <c r="C106" s="70"/>
     </row>
     <row r="107" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="129" t="s">
+      <c r="A107" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="B107" s="130">
+      <c r="B107" s="128">
         <f>'Copia de PRORRATEO'!H37</f>
         <v>2958103.33</v>
       </c>
       <c r="C107" s="69"/>
     </row>
-    <row r="108" spans="1:26" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="129" t="s">
+    <row r="108" spans="1:26" s="133" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="127" t="s">
         <v>157</v>
       </c>
-      <c r="B108" s="178"/>
-      <c r="C108" s="177"/>
+      <c r="B108" s="174"/>
+      <c r="C108" s="173"/>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="71" t="s">
@@ -4432,24 +4428,24 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" s="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="B111" s="219">
+      <c r="B111" s="211">
         <v>90000</v>
       </c>
-      <c r="C111" s="177"/>
-    </row>
-    <row r="112" spans="1:26" s="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C111" s="173"/>
+    </row>
+    <row r="112" spans="1:26" s="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="B112" s="219">
+      <c r="B112" s="211">
         <f>228000-132000</f>
         <v>96000</v>
       </c>
-      <c r="C112" s="177"/>
+      <c r="C112" s="173"/>
     </row>
     <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="75" t="s">
@@ -4624,34 +4620,34 @@
     <row r="123" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="266" t="s">
+      <c r="A125" s="230" t="s">
         <v>53</v>
       </c>
-      <c r="B125" s="239"/>
-      <c r="C125" s="239"/>
+      <c r="B125" s="231"/>
+      <c r="C125" s="231"/>
     </row>
     <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="239"/>
-      <c r="B126" s="239"/>
-      <c r="C126" s="239"/>
+      <c r="A126" s="231"/>
+      <c r="B126" s="231"/>
+      <c r="C126" s="231"/>
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="13"/>
-      <c r="B127" s="225"/>
+      <c r="B127" s="217"/>
       <c r="C127" s="31">
         <v>11948.17</v>
       </c>
     </row>
     <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
-      <c r="B128" s="153"/>
+      <c r="B128" s="149"/>
       <c r="C128" s="31">
         <v>52000</v>
       </c>
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="84"/>
-      <c r="B129" s="153"/>
+      <c r="B129" s="149"/>
       <c r="C129" s="31">
         <v>61209</v>
       </c>
@@ -4681,7 +4677,7 @@
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="71"/>
-      <c r="B130" s="153"/>
+      <c r="B130" s="149"/>
       <c r="C130" s="31">
         <v>40000</v>
       </c>
@@ -4713,7 +4709,7 @@
       <c r="A131" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="B131" s="154">
+      <c r="B131" s="150">
         <f>SUM(B127:B130)</f>
         <v>0</v>
       </c>
@@ -5593,6 +5589,18 @@
     <sortCondition ref="E39:E40"/>
   </sortState>
   <mergeCells count="24">
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A58:B59"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A125:C126"/>
     <mergeCell ref="D58:D59"/>
     <mergeCell ref="A56:B56"/>
@@ -5605,18 +5613,6 @@
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A99:B100"/>
     <mergeCell ref="A102:B103"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A58:B59"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A53:B53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5657,16 +5653,16 @@
       <c r="C1" s="88"/>
       <c r="D1" s="88"/>
       <c r="E1" s="88"/>
-      <c r="F1" s="244"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="231"/>
       <c r="P1" s="88"/>
       <c r="Q1" s="88"/>
     </row>
@@ -5690,7 +5686,7 @@
       </c>
       <c r="M2" s="88"/>
       <c r="N2" s="88"/>
-      <c r="O2" s="180">
+      <c r="O2" s="176">
         <v>3000000</v>
       </c>
       <c r="P2" s="90"/>
@@ -5719,80 +5715,80 @@
       <c r="Q3" s="92"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="233" t="s">
+      <c r="A4" s="270" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="259" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="235" t="s">
+      <c r="C4" s="264" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="235" t="s">
+      <c r="D4" s="264" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="236" t="s">
+      <c r="E4" s="268" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="235" t="s">
+      <c r="F4" s="264" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="235" t="s">
+      <c r="G4" s="264" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="235" t="s">
+      <c r="H4" s="264" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="236" t="s">
+      <c r="I4" s="268" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="248" t="s">
+      <c r="J4" s="269" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="240" t="s">
+      <c r="K4" s="257" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="243" t="s">
+      <c r="L4" s="261" t="s">
         <v>67</v>
       </c>
-      <c r="M4" s="240" t="s">
+      <c r="M4" s="257" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="245" t="s">
+      <c r="N4" s="265" t="s">
         <v>69</v>
       </c>
       <c r="O4" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="P4" s="247" t="s">
+      <c r="P4" s="267" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" s="243" t="s">
+      <c r="Q4" s="261" t="s">
         <v>72</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="234"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="234"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="246"/>
+      <c r="A5" s="262"/>
+      <c r="B5" s="260"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="262"/>
+      <c r="M5" s="258"/>
+      <c r="N5" s="266"/>
       <c r="O5" s="94" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="234"/>
+      <c r="P5" s="260"/>
+      <c r="Q5" s="262"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -5816,7 +5812,7 @@
       <c r="G6" s="97">
         <v>33000.01</v>
       </c>
-      <c r="H6" s="137">
+      <c r="H6" s="135">
         <f t="shared" ref="H6:H12" si="0">G6</f>
         <v>33000.01</v>
       </c>
@@ -5840,7 +5836,7 @@
       <c r="N6" s="101">
         <v>0</v>
       </c>
-      <c r="O6" s="125">
+      <c r="O6" s="102">
         <f>ROUND(SUM(J6:N6),0) + R6</f>
         <v>33000.01</v>
       </c>
@@ -5848,7 +5844,7 @@
         <f t="shared" ref="P6:P36" si="3">ROUND(O6*6% + O6,0) + R6</f>
         <v>34980.01</v>
       </c>
-      <c r="Q6" s="126">
+      <c r="Q6" s="103">
         <f t="shared" ref="Q6:Q36" si="4">ROUND(O6*3%,0) + O6</f>
         <v>33990.01</v>
       </c>
@@ -5860,33 +5856,33 @@
       <c r="A7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="170">
+      <c r="B7" s="166">
         <v>2</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="167" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="172"/>
-      <c r="F7" s="173">
+      <c r="E7" s="168"/>
+      <c r="F7" s="169">
         <v>0.9</v>
       </c>
-      <c r="G7" s="143">
+      <c r="G7" s="141">
         <v>27000.02</v>
       </c>
-      <c r="H7" s="137"/>
+      <c r="H7" s="135"/>
       <c r="I7" s="99"/>
-      <c r="J7" s="144">
+      <c r="J7" s="142">
         <f t="shared" si="1"/>
         <v>27000.02</v>
       </c>
-      <c r="K7" s="144">
+      <c r="K7" s="142">
         <f t="shared" si="2"/>
         <v>810.00059999999996</v>
       </c>
-      <c r="L7" s="143">
+      <c r="L7" s="141">
         <f t="shared" ref="L7:L34" si="5">O$3*F7%</f>
         <v>0</v>
       </c>
@@ -5894,18 +5890,18 @@
         <f t="shared" ref="M7:M34" si="6">O$2*F7%</f>
         <v>27000.000000000004</v>
       </c>
-      <c r="N7" s="145">
+      <c r="N7" s="143">
         <v>0</v>
       </c>
-      <c r="O7" s="146">
+      <c r="O7" s="271">
         <f t="shared" ref="O7:O34" si="7">ROUND(SUM(J7:N7),0) + R7</f>
         <v>54810.02</v>
       </c>
-      <c r="P7" s="147">
+      <c r="P7" s="144">
         <f t="shared" si="3"/>
         <v>58099.02</v>
       </c>
-      <c r="Q7" s="148">
+      <c r="Q7" s="274">
         <f t="shared" si="4"/>
         <v>56454.02</v>
       </c>
@@ -5919,38 +5915,38 @@
       <c r="A8" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="170">
+      <c r="B8" s="166">
         <v>3</v>
       </c>
-      <c r="C8" s="171" t="s">
+      <c r="C8" s="167" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="171" t="s">
+      <c r="D8" s="167" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="172" t="s">
+      <c r="E8" s="168" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="173">
+      <c r="F8" s="169">
         <v>0.8</v>
       </c>
-      <c r="G8" s="143">
+      <c r="G8" s="141">
         <v>74182.03</v>
       </c>
-      <c r="H8" s="137">
+      <c r="H8" s="135">
         <f>G8</f>
         <v>74182.03</v>
       </c>
       <c r="I8" s="99"/>
-      <c r="J8" s="144">
+      <c r="J8" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="144">
+      <c r="K8" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L8" s="143">
+      <c r="L8" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5958,18 +5954,18 @@
         <f t="shared" si="6"/>
         <v>24000</v>
       </c>
-      <c r="N8" s="145">
+      <c r="N8" s="143">
         <v>0</v>
       </c>
-      <c r="O8" s="146">
+      <c r="O8" s="271">
         <f t="shared" si="7"/>
         <v>24000.03</v>
       </c>
-      <c r="P8" s="147">
+      <c r="P8" s="144">
         <f t="shared" si="3"/>
         <v>25440.03</v>
       </c>
-      <c r="Q8" s="148">
+      <c r="Q8" s="274">
         <f t="shared" si="4"/>
         <v>24720.03</v>
       </c>
@@ -5982,36 +5978,36 @@
       <c r="A9" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="170">
+      <c r="B9" s="166">
         <v>4</v>
       </c>
-      <c r="C9" s="171" t="s">
+      <c r="C9" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="171" t="s">
+      <c r="D9" s="167" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="172"/>
-      <c r="F9" s="173">
+      <c r="E9" s="168"/>
+      <c r="F9" s="169">
         <v>0.8</v>
       </c>
-      <c r="G9" s="143">
+      <c r="G9" s="141">
         <v>24000.04</v>
       </c>
-      <c r="H9" s="137">
+      <c r="H9" s="135">
         <f t="shared" si="0"/>
         <v>24000.04</v>
       </c>
       <c r="I9" s="99"/>
-      <c r="J9" s="144">
+      <c r="J9" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="144">
+      <c r="K9" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L9" s="143">
+      <c r="L9" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6019,18 +6015,18 @@
         <f t="shared" si="6"/>
         <v>24000</v>
       </c>
-      <c r="N9" s="145">
+      <c r="N9" s="143">
         <v>0</v>
       </c>
-      <c r="O9" s="146">
+      <c r="O9" s="271">
         <f t="shared" si="7"/>
         <v>24000.04</v>
       </c>
-      <c r="P9" s="147">
+      <c r="P9" s="144">
         <f t="shared" si="3"/>
         <v>25440.04</v>
       </c>
-      <c r="Q9" s="148">
+      <c r="Q9" s="274">
         <f t="shared" si="4"/>
         <v>24720.04</v>
       </c>
@@ -6043,38 +6039,38 @@
       <c r="A10" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="170">
+      <c r="B10" s="166">
         <v>5</v>
       </c>
-      <c r="C10" s="171" t="s">
+      <c r="C10" s="167" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="171" t="s">
+      <c r="D10" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="172" t="s">
+      <c r="E10" s="168" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="173">
+      <c r="F10" s="169">
         <v>0.5</v>
       </c>
-      <c r="G10" s="143">
+      <c r="G10" s="141">
         <v>15000.05</v>
       </c>
-      <c r="H10" s="137">
+      <c r="H10" s="135">
         <f t="shared" si="0"/>
         <v>15000.05</v>
       </c>
       <c r="I10" s="99"/>
-      <c r="J10" s="144">
+      <c r="J10" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="144">
+      <c r="K10" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" s="143">
+      <c r="L10" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6082,18 +6078,18 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="N10" s="145">
+      <c r="N10" s="143">
         <v>0</v>
       </c>
-      <c r="O10" s="146">
+      <c r="O10" s="271">
         <f t="shared" si="7"/>
         <v>15000.05</v>
       </c>
-      <c r="P10" s="147">
+      <c r="P10" s="144">
         <f t="shared" si="3"/>
         <v>15900.05</v>
       </c>
-      <c r="Q10" s="148">
+      <c r="Q10" s="274">
         <f t="shared" si="4"/>
         <v>15450.05</v>
       </c>
@@ -6106,36 +6102,36 @@
       <c r="A11" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="170">
+      <c r="B11" s="166">
         <v>6</v>
       </c>
-      <c r="C11" s="171" t="s">
+      <c r="C11" s="167" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="171" t="s">
+      <c r="D11" s="167" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="174"/>
-      <c r="F11" s="173">
+      <c r="E11" s="170"/>
+      <c r="F11" s="169">
         <v>0.5</v>
       </c>
-      <c r="G11" s="143">
+      <c r="G11" s="141">
         <v>15000.06</v>
       </c>
-      <c r="H11" s="137">
+      <c r="H11" s="135">
         <f t="shared" si="0"/>
         <v>15000.06</v>
       </c>
       <c r="I11" s="99"/>
-      <c r="J11" s="144">
+      <c r="J11" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="144">
+      <c r="K11" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L11" s="143">
+      <c r="L11" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6143,18 +6139,18 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="N11" s="145">
+      <c r="N11" s="143">
         <v>0</v>
       </c>
-      <c r="O11" s="146">
+      <c r="O11" s="271">
         <f t="shared" si="7"/>
         <v>15000.06</v>
       </c>
-      <c r="P11" s="147">
+      <c r="P11" s="144">
         <f t="shared" si="3"/>
         <v>15900.06</v>
       </c>
-      <c r="Q11" s="148">
+      <c r="Q11" s="274">
         <f t="shared" si="4"/>
         <v>15450.06</v>
       </c>
@@ -6167,38 +6163,38 @@
       <c r="A12" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="170">
+      <c r="B12" s="166">
         <v>7</v>
       </c>
-      <c r="C12" s="171" t="s">
+      <c r="C12" s="167" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="171" t="s">
+      <c r="D12" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="172" t="s">
+      <c r="E12" s="168" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="173">
+      <c r="F12" s="169">
         <v>0.5</v>
       </c>
-      <c r="G12" s="143">
+      <c r="G12" s="141">
         <v>15450.07</v>
       </c>
-      <c r="H12" s="137">
+      <c r="H12" s="135">
         <f t="shared" si="0"/>
         <v>15450.07</v>
       </c>
       <c r="I12" s="99"/>
-      <c r="J12" s="144">
+      <c r="J12" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="144">
+      <c r="K12" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6206,18 +6202,18 @@
         <f t="shared" si="6"/>
         <v>15000</v>
       </c>
-      <c r="N12" s="145">
+      <c r="N12" s="143">
         <v>0</v>
       </c>
-      <c r="O12" s="146">
+      <c r="O12" s="271">
         <f t="shared" si="7"/>
         <v>15000.07</v>
       </c>
-      <c r="P12" s="147">
+      <c r="P12" s="144">
         <f t="shared" si="3"/>
         <v>15900.07</v>
       </c>
-      <c r="Q12" s="148">
+      <c r="Q12" s="274">
         <f t="shared" si="4"/>
         <v>15450.07</v>
       </c>
@@ -6230,55 +6226,55 @@
       <c r="A13" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="202" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="209">
+      <c r="C13" s="203">
         <v>1</v>
       </c>
-      <c r="D13" s="209" t="s">
+      <c r="D13" s="203" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="210" t="s">
+      <c r="E13" s="204" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="211">
+      <c r="F13" s="205">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G13" s="212">
+      <c r="G13" s="206">
         <v>132000.07999999999</v>
       </c>
-      <c r="H13" s="230">
+      <c r="H13" s="222">
         <f>228000-RESUMEN!B112</f>
         <v>132000</v>
       </c>
-      <c r="I13" s="213"/>
-      <c r="J13" s="214">
+      <c r="I13" s="207"/>
+      <c r="J13" s="208">
         <f t="shared" si="1"/>
         <v>7.9999999987194315E-2</v>
       </c>
-      <c r="K13" s="214">
+      <c r="K13" s="208">
         <f t="shared" si="2"/>
         <v>2.3999999996158292E-3</v>
       </c>
-      <c r="L13" s="212">
+      <c r="L13" s="206">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M13" s="214">
+      <c r="M13" s="208">
         <f t="shared" si="6"/>
         <v>132000</v>
       </c>
-      <c r="N13" s="215"/>
-      <c r="O13" s="216">
+      <c r="N13" s="209"/>
+      <c r="O13" s="272">
         <f t="shared" si="7"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="P13" s="217">
+      <c r="P13" s="210">
         <f t="shared" si="3"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="Q13" s="218">
+      <c r="Q13" s="275">
         <f t="shared" si="4"/>
         <v>135960.07999999999</v>
       </c>
@@ -6308,7 +6304,7 @@
       <c r="G14" s="97">
         <v>135000.09</v>
       </c>
-      <c r="H14" s="137">
+      <c r="H14" s="135">
         <f>159000-H9</f>
         <v>134999.96</v>
       </c>
@@ -6332,7 +6328,7 @@
       <c r="N14" s="101">
         <v>0</v>
       </c>
-      <c r="O14" s="125">
+      <c r="O14" s="102">
         <f t="shared" si="7"/>
         <v>135000.09</v>
       </c>
@@ -6340,7 +6336,7 @@
         <f t="shared" si="3"/>
         <v>143100.09</v>
       </c>
-      <c r="Q14" s="126">
+      <c r="Q14" s="103">
         <f t="shared" si="4"/>
         <v>139050.09</v>
       </c>
@@ -6348,7 +6344,7 @@
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
-      <c r="U14" s="152" t="s">
+      <c r="U14" s="148" t="s">
         <v>97</v>
       </c>
     </row>
@@ -6375,7 +6371,7 @@
       <c r="G15" s="97">
         <v>135000.1</v>
       </c>
-      <c r="H15" s="231"/>
+      <c r="H15" s="223"/>
       <c r="I15" s="99"/>
       <c r="J15" s="100">
         <f t="shared" si="1"/>
@@ -6396,7 +6392,7 @@
       <c r="N15" s="101">
         <v>0</v>
       </c>
-      <c r="O15" s="125">
+      <c r="O15" s="102">
         <f t="shared" si="7"/>
         <v>274050.09999999998</v>
       </c>
@@ -6404,7 +6400,7 @@
         <f t="shared" si="3"/>
         <v>290493.09999999998</v>
       </c>
-      <c r="Q15" s="126">
+      <c r="Q15" s="103">
         <f t="shared" si="4"/>
         <v>282272.09999999998</v>
       </c>
@@ -6436,7 +6432,7 @@
       <c r="G16" s="97">
         <v>93000.11</v>
       </c>
-      <c r="H16" s="137">
+      <c r="H16" s="135">
         <f>G16</f>
         <v>93000.11</v>
       </c>
@@ -6460,7 +6456,7 @@
       <c r="N16" s="101">
         <v>0</v>
       </c>
-      <c r="O16" s="125">
+      <c r="O16" s="102">
         <f t="shared" si="7"/>
         <v>93000.11</v>
       </c>
@@ -6468,7 +6464,7 @@
         <f t="shared" si="3"/>
         <v>98580.11</v>
       </c>
-      <c r="Q16" s="126">
+      <c r="Q16" s="103">
         <f t="shared" si="4"/>
         <v>95790.11</v>
       </c>
@@ -6481,55 +6477,55 @@
       <c r="A17" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="170" t="s">
+      <c r="B17" s="166" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="171">
+      <c r="C17" s="167">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="D17" s="171" t="s">
+      <c r="D17" s="167" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="172" t="s">
+      <c r="E17" s="168" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="173">
+      <c r="F17" s="169">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G17" s="143">
+      <c r="G17" s="141">
         <v>354433.12</v>
       </c>
-      <c r="H17" s="137"/>
+      <c r="H17" s="135"/>
       <c r="I17" s="99"/>
-      <c r="J17" s="144">
+      <c r="J17" s="142">
         <f t="shared" si="1"/>
         <v>354433.12</v>
       </c>
-      <c r="K17" s="144">
+      <c r="K17" s="142">
         <f t="shared" si="2"/>
         <v>10632.9936</v>
       </c>
-      <c r="L17" s="143">
+      <c r="L17" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M17" s="144">
+      <c r="M17" s="142">
         <f t="shared" si="6"/>
         <v>132000</v>
       </c>
-      <c r="N17" s="145">
+      <c r="N17" s="143">
         <v>0</v>
       </c>
-      <c r="O17" s="146">
+      <c r="O17" s="271">
         <f t="shared" si="7"/>
         <v>497066.12</v>
       </c>
-      <c r="P17" s="147">
+      <c r="P17" s="144">
         <f t="shared" si="3"/>
         <v>526890.12</v>
       </c>
-      <c r="Q17" s="148">
+      <c r="Q17" s="274">
         <f t="shared" si="4"/>
         <v>511978.12</v>
       </c>
@@ -6542,57 +6538,57 @@
       <c r="A18" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="170" t="s">
+      <c r="B18" s="166" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="171">
+      <c r="C18" s="167">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="D18" s="171" t="s">
+      <c r="D18" s="167" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="172" t="s">
+      <c r="E18" s="168" t="s">
         <v>185</v>
       </c>
-      <c r="F18" s="173">
+      <c r="F18" s="169">
         <v>4.5</v>
       </c>
-      <c r="G18" s="143">
+      <c r="G18" s="141">
         <v>131197.13</v>
       </c>
-      <c r="H18" s="137">
+      <c r="H18" s="135">
         <v>135133</v>
       </c>
       <c r="I18" s="99"/>
-      <c r="J18" s="144">
+      <c r="J18" s="142">
         <f t="shared" si="1"/>
         <v>-3935.8699999999953</v>
       </c>
-      <c r="K18" s="144">
+      <c r="K18" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="143">
+      <c r="L18" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M18" s="144">
+      <c r="M18" s="142">
         <f t="shared" si="6"/>
         <v>135000</v>
       </c>
-      <c r="N18" s="145">
+      <c r="N18" s="143">
         <v>0</v>
       </c>
-      <c r="O18" s="146">
+      <c r="O18" s="271">
         <f t="shared" si="7"/>
         <v>131064.13</v>
       </c>
-      <c r="P18" s="147">
+      <c r="P18" s="144">
         <f t="shared" si="3"/>
         <v>138928.13</v>
       </c>
-      <c r="Q18" s="148">
+      <c r="Q18" s="274">
         <f t="shared" si="4"/>
         <v>134996.13</v>
       </c>
@@ -6600,7 +6596,7 @@
         <f t="shared" si="8"/>
         <v>0.12999999999999998</v>
       </c>
-      <c r="T18" s="224" t="s">
+      <c r="T18" s="216" t="s">
         <v>160</v>
       </c>
     </row>
@@ -6625,7 +6621,7 @@
       <c r="G19" s="97">
         <v>135000.14000000001</v>
       </c>
-      <c r="H19" s="137">
+      <c r="H19" s="135">
         <f>G19</f>
         <v>135000.14000000001</v>
       </c>
@@ -6649,7 +6645,7 @@
       <c r="N19" s="101">
         <v>0</v>
       </c>
-      <c r="O19" s="125">
+      <c r="O19" s="102">
         <f t="shared" si="7"/>
         <v>135000.14000000001</v>
       </c>
@@ -6657,7 +6653,7 @@
         <f t="shared" si="3"/>
         <v>143100.14000000001</v>
       </c>
-      <c r="Q19" s="126">
+      <c r="Q19" s="103">
         <f t="shared" si="4"/>
         <v>139050.14000000001</v>
       </c>
@@ -6687,7 +6683,7 @@
       <c r="G20" s="97">
         <v>93000.15</v>
       </c>
-      <c r="H20" s="137">
+      <c r="H20" s="135">
         <f>G20</f>
         <v>93000.15</v>
       </c>
@@ -6711,7 +6707,7 @@
       <c r="N20" s="101">
         <v>0</v>
       </c>
-      <c r="O20" s="125">
+      <c r="O20" s="102">
         <f t="shared" si="7"/>
         <v>93000.15</v>
       </c>
@@ -6719,7 +6715,7 @@
         <f t="shared" si="3"/>
         <v>98580.15</v>
       </c>
-      <c r="Q20" s="126">
+      <c r="Q20" s="103">
         <f t="shared" si="4"/>
         <v>95790.15</v>
       </c>
@@ -6751,7 +6747,7 @@
       <c r="G21" s="97">
         <v>132000.16</v>
       </c>
-      <c r="H21" s="137">
+      <c r="H21" s="135">
         <f>G21</f>
         <v>132000.16</v>
       </c>
@@ -6775,7 +6771,7 @@
       <c r="N21" s="101">
         <v>0</v>
       </c>
-      <c r="O21" s="125">
+      <c r="O21" s="102">
         <f t="shared" si="7"/>
         <v>132000.16</v>
       </c>
@@ -6783,7 +6779,7 @@
         <f t="shared" si="3"/>
         <v>139920.16</v>
       </c>
-      <c r="Q21" s="126">
+      <c r="Q21" s="103">
         <f t="shared" si="4"/>
         <v>135960.16</v>
       </c>
@@ -6816,7 +6812,7 @@
       <c r="G22" s="98">
         <v>138090.17000000001</v>
       </c>
-      <c r="H22" s="137">
+      <c r="H22" s="135">
         <f>G22</f>
         <v>138090.17000000001</v>
       </c>
@@ -6840,7 +6836,7 @@
       <c r="N22" s="101">
         <v>0</v>
       </c>
-      <c r="O22" s="125">
+      <c r="O22" s="102">
         <f t="shared" si="7"/>
         <v>135000.17000000001</v>
       </c>
@@ -6848,7 +6844,7 @@
         <f t="shared" si="3"/>
         <v>143100.17000000001</v>
       </c>
-      <c r="Q22" s="126">
+      <c r="Q22" s="103">
         <f t="shared" si="4"/>
         <v>139050.17000000001</v>
       </c>
@@ -6856,8 +6852,8 @@
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
-      <c r="T22" s="151"/>
-      <c r="U22" s="175" t="s">
+      <c r="T22" s="147"/>
+      <c r="U22" s="171" t="s">
         <v>122</v>
       </c>
     </row>
@@ -6879,22 +6875,22 @@
       <c r="F23" s="96">
         <v>4.5</v>
       </c>
-      <c r="G23" s="143">
+      <c r="G23" s="141">
         <v>130950.18</v>
       </c>
-      <c r="H23" s="137">
+      <c r="H23" s="135">
         <v>134879</v>
       </c>
       <c r="I23" s="99"/>
-      <c r="J23" s="144">
+      <c r="J23" s="142">
         <f t="shared" si="1"/>
         <v>-3928.820000000007</v>
       </c>
-      <c r="K23" s="144">
+      <c r="K23" s="142">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="143">
+      <c r="L23" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6902,18 +6898,18 @@
         <f t="shared" si="6"/>
         <v>135000</v>
       </c>
-      <c r="N23" s="145">
+      <c r="N23" s="143">
         <v>0</v>
       </c>
-      <c r="O23" s="146">
+      <c r="O23" s="271">
         <f t="shared" si="7"/>
         <v>131071.18</v>
       </c>
-      <c r="P23" s="147">
+      <c r="P23" s="144">
         <f t="shared" si="3"/>
         <v>138935.18</v>
       </c>
-      <c r="Q23" s="148">
+      <c r="Q23" s="274">
         <f t="shared" si="4"/>
         <v>135003.18</v>
       </c>
@@ -6921,7 +6917,7 @@
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="T23" s="151"/>
+      <c r="T23" s="147"/>
     </row>
     <row r="24" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -6946,7 +6942,7 @@
       <c r="G24" s="97">
         <v>290503.19</v>
       </c>
-      <c r="H24" s="137">
+      <c r="H24" s="135">
         <f>365000-H8</f>
         <v>290817.96999999997</v>
       </c>
@@ -6970,7 +6966,7 @@
       <c r="N24" s="101">
         <v>0</v>
       </c>
-      <c r="O24" s="125">
+      <c r="O24" s="102">
         <f t="shared" si="7"/>
         <v>92685.19</v>
       </c>
@@ -6978,7 +6974,7 @@
         <f t="shared" si="3"/>
         <v>98246.19</v>
       </c>
-      <c r="Q24" s="126">
+      <c r="Q24" s="103">
         <f t="shared" si="4"/>
         <v>95466.19</v>
       </c>
@@ -6986,30 +6982,30 @@
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
-      <c r="T24" s="151"/>
+      <c r="T24" s="147"/>
     </row>
     <row r="25" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="170" t="s">
+      <c r="B25" s="166" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="171">
+      <c r="C25" s="167">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="D25" s="171" t="s">
+      <c r="D25" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="174"/>
-      <c r="F25" s="173">
+      <c r="E25" s="170"/>
+      <c r="F25" s="169">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G25" s="143">
+      <c r="G25" s="141">
         <v>135916.20000000001</v>
       </c>
-      <c r="H25" s="137">
+      <c r="H25" s="135">
         <v>133000</v>
       </c>
       <c r="I25" s="99"/>
@@ -7017,11 +7013,11 @@
         <f t="shared" si="1"/>
         <v>2916.2000000000116</v>
       </c>
-      <c r="K25" s="144">
+      <c r="K25" s="142">
         <f t="shared" si="2"/>
         <v>87.486000000000345</v>
       </c>
-      <c r="L25" s="143">
+      <c r="L25" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7029,18 +7025,18 @@
         <f t="shared" si="6"/>
         <v>132000</v>
       </c>
-      <c r="N25" s="145">
+      <c r="N25" s="143">
         <v>0</v>
       </c>
-      <c r="O25" s="146">
+      <c r="O25" s="271">
         <f t="shared" si="7"/>
         <v>135004.20000000001</v>
       </c>
-      <c r="P25" s="147">
+      <c r="P25" s="144">
         <f t="shared" si="3"/>
         <v>143104.20000000001</v>
       </c>
-      <c r="Q25" s="148">
+      <c r="Q25" s="274">
         <f t="shared" si="4"/>
         <v>139054.20000000001</v>
       </c>
@@ -7048,11 +7044,11 @@
         <f t="shared" si="8"/>
         <v>0.20000000000000004</v>
       </c>
-      <c r="T25" s="152" t="s">
+      <c r="T25" s="148" t="s">
         <v>130</v>
       </c>
-      <c r="U25" s="169"/>
-      <c r="V25" s="152"/>
+      <c r="U25" s="165"/>
+      <c r="V25" s="148"/>
     </row>
     <row r="26" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
@@ -7077,7 +7073,7 @@
       <c r="G26" s="97">
         <v>135000.21</v>
       </c>
-      <c r="H26" s="137">
+      <c r="H26" s="135">
         <f>168000-H6</f>
         <v>134999.99</v>
       </c>
@@ -7101,7 +7097,7 @@
       <c r="N26" s="101">
         <v>0</v>
       </c>
-      <c r="O26" s="125">
+      <c r="O26" s="102">
         <f t="shared" si="7"/>
         <v>135000.21</v>
       </c>
@@ -7109,7 +7105,7 @@
         <f t="shared" si="3"/>
         <v>143100.21</v>
       </c>
-      <c r="Q26" s="126">
+      <c r="Q26" s="103">
         <f t="shared" si="4"/>
         <v>139050.21</v>
       </c>
@@ -7117,7 +7113,7 @@
         <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
-      <c r="T26" s="151"/>
+      <c r="T26" s="147"/>
     </row>
     <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
@@ -7142,7 +7138,7 @@
       <c r="G27" s="97">
         <v>339600.22</v>
       </c>
-      <c r="H27" s="137">
+      <c r="H27" s="135">
         <f>150000-H12</f>
         <v>134549.93</v>
       </c>
@@ -7166,7 +7162,7 @@
       <c r="N27" s="101">
         <v>0</v>
       </c>
-      <c r="O27" s="125">
+      <c r="O27" s="102">
         <f t="shared" si="7"/>
         <v>346202.22</v>
       </c>
@@ -7174,7 +7170,7 @@
         <f t="shared" si="3"/>
         <v>366974.22</v>
       </c>
-      <c r="Q27" s="126">
+      <c r="Q27" s="103">
         <f t="shared" si="4"/>
         <v>356588.22</v>
       </c>
@@ -7182,64 +7178,64 @@
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
-      <c r="T27" s="221"/>
+      <c r="T27" s="213"/>
     </row>
     <row r="28" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="170" t="s">
+      <c r="B28" s="166" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="171">
+      <c r="C28" s="167">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="D28" s="171" t="s">
+      <c r="D28" s="167" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="172" t="s">
+      <c r="E28" s="168" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="173">
+      <c r="F28" s="169">
         <v>3.1</v>
       </c>
-      <c r="G28" s="143">
+      <c r="G28" s="141">
         <v>93000.23</v>
       </c>
-      <c r="H28" s="137">
+      <c r="H28" s="135">
         <f>93000</f>
         <v>93000</v>
       </c>
       <c r="I28" s="99"/>
-      <c r="J28" s="144">
+      <c r="J28" s="142">
         <f t="shared" si="1"/>
         <v>0.22999999999592546</v>
       </c>
-      <c r="K28" s="144">
+      <c r="K28" s="142">
         <f t="shared" si="2"/>
         <v>6.8999999998777635E-3</v>
       </c>
-      <c r="L28" s="143">
+      <c r="L28" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M28" s="144">
+      <c r="M28" s="142">
         <f t="shared" si="6"/>
         <v>93000</v>
       </c>
-      <c r="N28" s="145">
+      <c r="N28" s="143">
         <v>0</v>
       </c>
-      <c r="O28" s="146">
+      <c r="O28" s="271">
         <f t="shared" si="7"/>
         <v>93000.23</v>
       </c>
-      <c r="P28" s="147">
+      <c r="P28" s="144">
         <f t="shared" si="3"/>
         <v>98580.23</v>
       </c>
-      <c r="Q28" s="148">
+      <c r="Q28" s="274">
         <f t="shared" si="4"/>
         <v>95790.23</v>
       </c>
@@ -7269,7 +7265,7 @@
       <c r="G29" s="97">
         <v>203996.24</v>
       </c>
-      <c r="H29" s="137">
+      <c r="H29" s="135">
         <f>219000-H11</f>
         <v>203999.94</v>
       </c>
@@ -7293,7 +7289,7 @@
       <c r="N29" s="101">
         <v>0</v>
       </c>
-      <c r="O29" s="125">
+      <c r="O29" s="102">
         <f t="shared" si="7"/>
         <v>203996.24</v>
       </c>
@@ -7301,7 +7297,7 @@
         <f t="shared" si="3"/>
         <v>216236.24</v>
       </c>
-      <c r="Q29" s="126">
+      <c r="Q29" s="103">
         <f t="shared" si="4"/>
         <v>210116.24</v>
       </c>
@@ -7314,63 +7310,63 @@
       <c r="A30" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="170" t="s">
+      <c r="B30" s="166" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="171">
+      <c r="C30" s="167">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="D30" s="171" t="s">
+      <c r="D30" s="167" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="174"/>
-      <c r="F30" s="173">
+      <c r="E30" s="170"/>
+      <c r="F30" s="169">
         <v>6.9</v>
       </c>
-      <c r="G30" s="143">
+      <c r="G30" s="141">
         <v>213397.25</v>
       </c>
-      <c r="H30" s="137">
+      <c r="H30" s="135">
         <f>207000</f>
         <v>207000</v>
       </c>
       <c r="I30" s="99"/>
-      <c r="J30" s="144">
+      <c r="J30" s="142">
         <f t="shared" si="1"/>
         <v>6397.25</v>
       </c>
-      <c r="K30" s="144">
+      <c r="K30" s="142">
         <f t="shared" si="2"/>
         <v>191.91749999999999</v>
       </c>
-      <c r="L30" s="143">
+      <c r="L30" s="141">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M30" s="144">
+      <c r="M30" s="142">
         <f t="shared" si="6"/>
         <v>207000.00000000003</v>
       </c>
-      <c r="N30" s="145"/>
-      <c r="O30" s="146">
+      <c r="N30" s="143"/>
+      <c r="O30" s="271">
         <f t="shared" si="7"/>
         <v>213589.25</v>
       </c>
-      <c r="P30" s="147">
+      <c r="P30" s="144">
         <f t="shared" si="3"/>
         <v>226405.25</v>
       </c>
-      <c r="Q30" s="148">
+      <c r="Q30" s="274">
         <f t="shared" si="4"/>
         <v>219997.25</v>
       </c>
-      <c r="R30" s="222">
+      <c r="R30" s="214">
         <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
-      <c r="S30" s="221"/>
-      <c r="T30" s="223"/>
+      <c r="S30" s="213"/>
+      <c r="T30" s="215"/>
     </row>
     <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
@@ -7395,7 +7391,7 @@
       <c r="G31" s="97">
         <v>135000.26</v>
       </c>
-      <c r="H31" s="137">
+      <c r="H31" s="135">
         <f>G31</f>
         <v>135000.26</v>
       </c>
@@ -7419,7 +7415,7 @@
       <c r="N31" s="101">
         <v>0</v>
       </c>
-      <c r="O31" s="125">
+      <c r="O31" s="102">
         <f t="shared" si="7"/>
         <v>135000.26</v>
       </c>
@@ -7427,7 +7423,7 @@
         <f t="shared" si="3"/>
         <v>143100.26</v>
       </c>
-      <c r="Q31" s="126">
+      <c r="Q31" s="103">
         <f t="shared" si="4"/>
         <v>139050.26</v>
       </c>
@@ -7459,7 +7455,7 @@
       <c r="G32" s="97">
         <v>194275.27</v>
       </c>
-      <c r="H32" s="232">
+      <c r="H32" s="224">
         <v>93000</v>
       </c>
       <c r="I32" s="99"/>
@@ -7482,7 +7478,7 @@
       <c r="N32" s="101">
         <v>0</v>
       </c>
-      <c r="O32" s="125">
+      <c r="O32" s="102">
         <f t="shared" si="7"/>
         <v>197314.27</v>
       </c>
@@ -7490,7 +7486,7 @@
         <f t="shared" si="3"/>
         <v>209153.27</v>
       </c>
-      <c r="Q32" s="126">
+      <c r="Q32" s="103">
         <f t="shared" si="4"/>
         <v>203233.27</v>
       </c>
@@ -7503,53 +7499,53 @@
       <c r="A33" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B33" s="181" t="s">
+      <c r="B33" s="177" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="182">
+      <c r="C33" s="178">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="D33" s="182" t="s">
+      <c r="D33" s="178" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="183" t="s">
+      <c r="E33" s="179" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="184">
+      <c r="F33" s="180">
         <v>4.5</v>
       </c>
-      <c r="G33" s="185">
+      <c r="G33" s="181">
         <v>135000.28</v>
       </c>
-      <c r="H33" s="230">
+      <c r="H33" s="222">
         <f>225000-RESUMEN!B111</f>
         <v>135000</v>
       </c>
-      <c r="I33" s="186"/>
-      <c r="J33" s="187">
+      <c r="I33" s="182"/>
+      <c r="J33" s="183">
         <f t="shared" si="1"/>
         <v>0.27999999999883585</v>
       </c>
-      <c r="K33" s="187"/>
-      <c r="L33" s="185">
+      <c r="K33" s="183"/>
+      <c r="L33" s="181">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M33" s="187">
+      <c r="M33" s="183">
         <f t="shared" si="6"/>
         <v>135000</v>
       </c>
-      <c r="N33" s="188"/>
-      <c r="O33" s="189">
+      <c r="N33" s="184"/>
+      <c r="O33" s="273">
         <f t="shared" si="7"/>
         <v>135000.28</v>
       </c>
-      <c r="P33" s="188">
+      <c r="P33" s="184">
         <f t="shared" si="3"/>
         <v>143100.28</v>
       </c>
-      <c r="Q33" s="190">
+      <c r="Q33" s="276">
         <f t="shared" si="4"/>
         <v>139050.28</v>
       </c>
@@ -7579,7 +7575,7 @@
       <c r="G34" s="97">
         <v>93000.29</v>
       </c>
-      <c r="H34" s="137">
+      <c r="H34" s="135">
         <f>G34</f>
         <v>93000.29</v>
       </c>
@@ -7603,7 +7599,7 @@
       <c r="N34" s="101">
         <v>0</v>
       </c>
-      <c r="O34" s="125">
+      <c r="O34" s="102">
         <f t="shared" si="7"/>
         <v>93000.29</v>
       </c>
@@ -7611,7 +7607,7 @@
         <f t="shared" si="3"/>
         <v>98580.29</v>
       </c>
-      <c r="Q34" s="126">
+      <c r="Q34" s="103">
         <f t="shared" si="4"/>
         <v>95790.29</v>
       </c>
@@ -7630,7 +7626,7 @@
       <c r="E35" s="104"/>
       <c r="F35" s="96"/>
       <c r="G35" s="97"/>
-      <c r="H35" s="137"/>
+      <c r="H35" s="135"/>
       <c r="I35" s="99"/>
       <c r="J35" s="100">
         <f t="shared" si="1"/>
@@ -7772,95 +7768,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="238" t="s">
+      <c r="D40" s="256" t="s">
         <v>158</v>
       </c>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
-      <c r="M40" s="239"/>
-      <c r="N40" s="239"/>
-      <c r="O40" s="239"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
+      <c r="O40" s="231"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="239"/>
-      <c r="E41" s="239"/>
-      <c r="F41" s="239"/>
-      <c r="G41" s="239"/>
-      <c r="H41" s="239"/>
-      <c r="I41" s="239"/>
-      <c r="J41" s="239"/>
-      <c r="K41" s="239"/>
-      <c r="L41" s="239"/>
-      <c r="M41" s="239"/>
-      <c r="N41" s="239"/>
-      <c r="O41" s="239"/>
+      <c r="D41" s="231"/>
+      <c r="E41" s="231"/>
+      <c r="F41" s="231"/>
+      <c r="G41" s="231"/>
+      <c r="H41" s="231"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="231"/>
+      <c r="N41" s="231"/>
+      <c r="O41" s="231"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="239"/>
-      <c r="E42" s="239"/>
-      <c r="F42" s="239"/>
-      <c r="G42" s="239"/>
-      <c r="H42" s="239"/>
-      <c r="I42" s="239"/>
-      <c r="J42" s="239"/>
-      <c r="K42" s="239"/>
-      <c r="L42" s="239"/>
-      <c r="M42" s="239"/>
-      <c r="N42" s="239"/>
-      <c r="O42" s="239"/>
+      <c r="D42" s="231"/>
+      <c r="E42" s="231"/>
+      <c r="F42" s="231"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="231"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="231"/>
+      <c r="O42" s="231"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="239"/>
-      <c r="E43" s="239"/>
-      <c r="F43" s="239"/>
-      <c r="G43" s="239"/>
-      <c r="H43" s="239"/>
-      <c r="I43" s="239"/>
-      <c r="J43" s="239"/>
-      <c r="K43" s="239"/>
-      <c r="L43" s="239"/>
-      <c r="M43" s="239"/>
-      <c r="N43" s="239"/>
-      <c r="O43" s="239"/>
+      <c r="D43" s="231"/>
+      <c r="E43" s="231"/>
+      <c r="F43" s="231"/>
+      <c r="G43" s="231"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="231"/>
+      <c r="N43" s="231"/>
+      <c r="O43" s="231"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="239"/>
-      <c r="E44" s="239"/>
-      <c r="F44" s="239"/>
-      <c r="G44" s="239"/>
-      <c r="H44" s="239"/>
-      <c r="I44" s="239"/>
-      <c r="J44" s="239"/>
-      <c r="K44" s="239"/>
-      <c r="L44" s="239"/>
-      <c r="M44" s="239"/>
-      <c r="N44" s="239"/>
-      <c r="O44" s="239"/>
+      <c r="D44" s="231"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="231"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="231"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="231"/>
+      <c r="O44" s="231"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="239"/>
-      <c r="E45" s="239"/>
-      <c r="F45" s="239"/>
-      <c r="G45" s="239"/>
-      <c r="H45" s="239"/>
-      <c r="I45" s="239"/>
-      <c r="J45" s="239"/>
-      <c r="K45" s="239"/>
-      <c r="L45" s="239"/>
-      <c r="M45" s="239"/>
-      <c r="N45" s="239"/>
-      <c r="O45" s="239"/>
+      <c r="D45" s="231"/>
+      <c r="E45" s="231"/>
+      <c r="F45" s="231"/>
+      <c r="G45" s="231"/>
+      <c r="H45" s="231"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="231"/>
+      <c r="N45" s="231"/>
+      <c r="O45" s="231"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13331,6 +13327,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13344,11 +13345,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
